--- a/inst/extdata/projects/Example/Configurations/Populations.xlsx
+++ b/inst/extdata/projects/Example/Configurations/Populations.xlsx
@@ -7,8 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Demographics" sheetId="1" r:id="rId1"/>
-    <sheet name="UserDefinedVariability" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -352,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -445,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TestPopulation</t>
+          <t>European_adults</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -459,10 +458,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -475,10 +474,10 @@
         </is>
       </c>
       <c r="L2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -487,88 +486,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CYP3A4:CYP3A4,CYP2D6:CYP2C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TestPopulation_noOnto</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>European_ICRP_2002</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="L3">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>41</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>kg/m²</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Container Path</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Distribution</t>
+          <t>CYP3A4:CYP3A4</t>
         </is>
       </c>
     </row>
